--- a/tumores/5. Hipofaringe.xlsx
+++ b/tumores/5. Hipofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C6DCCFB-4BEE-48EE-A073-2ABF6BE4174D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91A3C5D-5909-48E9-B645-3857B3773859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="92">
   <si>
     <t>T</t>
   </si>
@@ -223,15 +223,6 @@
     <t>🟦 T3: &gt;4 cm *</t>
   </si>
   <si>
-    <t>🟥 T4a: Invasión *</t>
-  </si>
-  <si>
-    <t>🟥 T4b: Enfermedad muy avanzada *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inv. </t>
-  </si>
-  <si>
     <t>NX: Ganglios no evaluables</t>
   </si>
   <si>
@@ -274,12 +265,6 @@
     <t>🟨 T2: &gt;2 cm pero ≤4 cm sin fijación de hemilaringe</t>
   </si>
   <si>
-    <t>Cartílago cricoides/tiroides, Hueso hioides, Glándula tiroidea, Músculo esofágico, Tejido blando del compartimiento central</t>
-  </si>
-  <si>
-    <t>Invasión de la fascia prevertebral, Atrapamiento de la arteria carótida, Compromiso de las estructuras mediastínicas</t>
-  </si>
-  <si>
     <t>&gt;2 cm y ≤4 cm sin fijacion de hemilaringe</t>
   </si>
   <si>
@@ -305,6 +290,18 @@
   </si>
   <si>
     <t>Ganglios bilaterales ≤6 cm y ENE-</t>
+  </si>
+  <si>
+    <t>🟥 T4a: Enfermedad localmente avanzada *</t>
+  </si>
+  <si>
+    <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
+  </si>
+  <si>
+    <t>Invasión del Cartílago cricoides/tiroides, Invasión del Hueso hioides, Invasión de Glándula tiroidea, Invasión del Músculo esofágico,Invasión del Tejido blando del compartimiento central</t>
+  </si>
+  <si>
+    <t>Invasión de la fascia prevertebral, Envuelve la carótida interna, Compromiso de las estructuras mediastínicas</t>
   </si>
 </sst>
 </file>
@@ -828,7 +825,7 @@
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="35.33203125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="42.44140625" style="5" customWidth="1"/>
     <col min="5" max="5" width="27.21875" style="5" customWidth="1"/>
     <col min="6" max="6" width="38.44140625" style="5" customWidth="1"/>
     <col min="7" max="16384" width="11.5546875" style="5"/>
@@ -892,14 +889,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -940,14 +937,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -965,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -974,28 +971,26 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="6"/>
-      <c r="C10" s="6" t="s">
-        <v>66</v>
+      <c r="C10" s="7" t="s">
+        <v>89</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>13</v>
@@ -1010,7 +1005,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>17</v>
@@ -1027,7 +1022,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>18</v>
@@ -1044,7 +1039,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>19</v>
@@ -1061,7 +1056,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
@@ -1078,13 +1073,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1095,13 +1090,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,13 +1107,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1129,13 +1124,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1146,7 +1141,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
@@ -1164,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>17</v>
@@ -1181,7 +1176,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>18</v>
@@ -1198,7 +1193,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>19</v>
@@ -1215,7 +1210,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>28</v>
@@ -1235,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>21</v>
@@ -1252,7 +1247,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>22</v>
@@ -1269,7 +1264,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>22</v>
@@ -1286,13 +1281,13 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1303,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>44</v>
@@ -1320,7 +1315,7 @@
         <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>35</v>
@@ -1334,7 +1329,7 @@
         <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>36</v>

--- a/tumores/5. Hipofaringe.xlsx
+++ b/tumores/5. Hipofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D91A3C5D-5909-48E9-B645-3857B3773859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DD1CB-1825-47B1-9F17-FD463509C883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -298,10 +298,10 @@
     <t>🟥 T4b: Enfermedad localmente muy avanzada *</t>
   </si>
   <si>
-    <t>Invasión del Cartílago cricoides/tiroides, Invasión del Hueso hioides, Invasión de Glándula tiroidea, Invasión del Músculo esofágico,Invasión del Tejido blando del compartimiento central</t>
-  </si>
-  <si>
     <t>Invasión de la fascia prevertebral, Envuelve la carótida interna, Compromiso de las estructuras mediastínicas</t>
+  </si>
+  <si>
+    <t>Invasión del cartílago cricoides/tiroides, Invasión del hueso hioides, Invasión de glándula tiroidea, Invasión del músculo esofágico, Invasión del tejido blando del compartimiento central</t>
   </si>
 </sst>
 </file>
@@ -947,7 +947,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
@@ -974,7 +974,7 @@
         <v>88</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -990,7 +990,7 @@
         <v>89</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>13</v>
@@ -1202,7 +1202,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>14</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>14</v>
       </c>

--- a/tumores/5. Hipofaringe.xlsx
+++ b/tumores/5. Hipofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DD1CB-1825-47B1-9F17-FD463509C883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8F7571-C857-42EC-B9EE-A5C8BCD6CD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -220,9 +220,6 @@
     <t>🟨 T2: Invasión más de un subsitio</t>
   </si>
   <si>
-    <t>🟦 T3: &gt;4 cm *</t>
-  </si>
-  <si>
     <t>NX: Ganglios no evaluables</t>
   </si>
   <si>
@@ -302,6 +299,9 @@
   </si>
   <si>
     <t>Invasión del cartílago cricoides/tiroides, Invasión del hueso hioides, Invasión de glándula tiroidea, Invasión del músculo esofágico, Invasión del tejido blando del compartimiento central</t>
+  </si>
+  <si>
+    <t>🟦 T3: &gt;4 cm (Fijación y/o diseminación) *</t>
   </si>
 </sst>
 </file>
@@ -889,14 +889,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -937,14 +937,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>40</v>
@@ -962,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -971,10 +971,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -987,10 +987,10 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>90</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>13</v>
@@ -1005,7 +1005,7 @@
         <v>15</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>17</v>
@@ -1022,7 +1022,7 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>18</v>
@@ -1039,7 +1039,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>19</v>
@@ -1056,7 +1056,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
@@ -1073,13 +1073,13 @@
         <v>15</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1090,13 +1090,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1107,13 +1107,13 @@
         <v>15</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,13 +1124,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1141,7 +1141,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D19" s="9"/>
       <c r="E19" s="9" t="s">
@@ -1159,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>17</v>
@@ -1176,7 +1176,7 @@
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>18</v>
@@ -1193,7 +1193,7 @@
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>19</v>
@@ -1210,7 +1210,7 @@
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>28</v>
@@ -1230,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>21</v>
@@ -1247,7 +1247,7 @@
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>22</v>
@@ -1264,7 +1264,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>22</v>
@@ -1281,13 +1281,13 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1298,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>44</v>
@@ -1315,7 +1315,7 @@
         <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>35</v>
@@ -1329,7 +1329,7 @@
         <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>36</v>

--- a/tumores/5. Hipofaringe.xlsx
+++ b/tumores/5. Hipofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8F7571-C857-42EC-B9EE-A5C8BCD6CD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6209C62-0C48-4289-A1E8-14E10B8E046F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>

--- a/tumores/5. Hipofaringe.xlsx
+++ b/tumores/5. Hipofaringe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6209C62-0C48-4289-A1E8-14E10B8E046F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DA4C51-53CF-4E9B-A22F-0DA9F65E36BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -247,9 +247,6 @@
     <t>🟨 N2a: Un solo ganglio  ipsilateral *</t>
   </si>
   <si>
-    <t>🟦 N3b: Uno o varios ganglios ENE+</t>
-  </si>
-  <si>
     <t>M0: Sin metástasis a distancia</t>
   </si>
   <si>
@@ -302,6 +299,9 @@
   </si>
   <si>
     <t>🟦 T3: &gt;4 cm (Fijación y/o diseminación) *</t>
+  </si>
+  <si>
+    <t>🟦 N3b: Uno o varios ganglios ENE+ *</t>
   </si>
 </sst>
 </file>
@@ -889,14 +889,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -937,14 +937,14 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -953,7 +953,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>40</v>
@@ -962,7 +962,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -971,10 +971,10 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -987,10 +987,10 @@
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>89</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>13</v>
@@ -1079,7 +1079,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -1096,7 +1096,7 @@
         <v>22</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1113,7 +1113,7 @@
         <v>22</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,13 +1124,13 @@
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1281,13 +1281,13 @@
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>23</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
@@ -1298,7 +1298,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>44</v>
@@ -1315,7 +1315,7 @@
         <v>34</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>35</v>
@@ -1329,7 +1329,7 @@
         <v>34</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>36</v>
